--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119740756</v>
+        <v>119741197</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587331</v>
+        <v>587297</v>
       </c>
       <c r="R3" t="n">
-        <v>6962854</v>
+        <v>6962990</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1000,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119740485</v>
+        <v>119740508</v>
       </c>
       <c r="B5" t="n">
-        <v>90846</v>
+        <v>91005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119740508</v>
+        <v>119740075</v>
       </c>
       <c r="B6" t="n">
         <v>91005</v>
@@ -1142,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587301</v>
+        <v>587322</v>
       </c>
       <c r="R6" t="n">
-        <v>6962793</v>
+        <v>6962672</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119740075</v>
+        <v>119740756</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,38 +1207,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587322</v>
+        <v>587331</v>
       </c>
       <c r="R7" t="n">
-        <v>6962672</v>
+        <v>6962854</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119740056</v>
+        <v>119740791</v>
       </c>
       <c r="B8" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,34 +1322,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587311</v>
+        <v>587344</v>
       </c>
       <c r="R8" t="n">
-        <v>6962674</v>
+        <v>6962881</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1408,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119740791</v>
+        <v>119740056</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,39 +1429,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587344</v>
+        <v>587311</v>
       </c>
       <c r="R9" t="n">
-        <v>6962881</v>
+        <v>6962674</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119740092</v>
+        <v>119740485</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587314</v>
+        <v>587301</v>
       </c>
       <c r="R10" t="n">
-        <v>6962674</v>
+        <v>6962793</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119741197</v>
+        <v>119740092</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,34 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587297</v>
+        <v>587314</v>
       </c>
       <c r="R11" t="n">
-        <v>6962990</v>
+        <v>6962674</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119741197</v>
+        <v>119740472</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587297</v>
+        <v>587294</v>
       </c>
       <c r="R3" t="n">
-        <v>6962990</v>
+        <v>6962768</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119740472</v>
+        <v>119740508</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587294</v>
+        <v>587301</v>
       </c>
       <c r="R4" t="n">
-        <v>6962768</v>
+        <v>6962793</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119740508</v>
+        <v>119741197</v>
       </c>
       <c r="B5" t="n">
-        <v>91005</v>
+        <v>90846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +1003,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587301</v>
+        <v>587297</v>
       </c>
       <c r="R5" t="n">
-        <v>6962793</v>
+        <v>6962990</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119740472</v>
+        <v>119740092</v>
       </c>
       <c r="B3" t="n">
         <v>90562</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587294</v>
+        <v>587314</v>
       </c>
       <c r="R3" t="n">
-        <v>6962768</v>
+        <v>6962674</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119740508</v>
+        <v>119740075</v>
       </c>
       <c r="B4" t="n">
         <v>91005</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587301</v>
+        <v>587322</v>
       </c>
       <c r="R4" t="n">
-        <v>6962793</v>
+        <v>6962672</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119741197</v>
+        <v>119740791</v>
       </c>
       <c r="B5" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587297</v>
+        <v>587344</v>
       </c>
       <c r="R5" t="n">
-        <v>6962990</v>
+        <v>6962881</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119740075</v>
+        <v>119740485</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>90846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587322</v>
+        <v>587301</v>
       </c>
       <c r="R6" t="n">
-        <v>6962672</v>
+        <v>6962793</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119740756</v>
+        <v>119740472</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,43 +1216,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587331</v>
+        <v>587294</v>
       </c>
       <c r="R7" t="n">
-        <v>6962854</v>
+        <v>6962768</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1306,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119740791</v>
+        <v>119740756</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,27 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587344</v>
+        <v>587331</v>
       </c>
       <c r="R8" t="n">
-        <v>6962881</v>
+        <v>6962854</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119740056</v>
+        <v>119741197</v>
       </c>
       <c r="B9" t="n">
         <v>90846</v>
@@ -1449,14 +1449,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587311</v>
+        <v>587297</v>
       </c>
       <c r="R9" t="n">
-        <v>6962674</v>
+        <v>6962990</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119740485</v>
+        <v>119740508</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>91005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,25 +1527,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119740092</v>
+        <v>119740056</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,21 +1633,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587314</v>
+        <v>587311</v>
       </c>
       <c r="R11" t="n">
         <v>6962674</v>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119740092</v>
+        <v>119740472</v>
       </c>
       <c r="B3" t="n">
         <v>90562</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587314</v>
+        <v>587294</v>
       </c>
       <c r="R3" t="n">
-        <v>6962674</v>
+        <v>6962768</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119740075</v>
+        <v>119741197</v>
       </c>
       <c r="B4" t="n">
-        <v>91005</v>
+        <v>90846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587322</v>
+        <v>587297</v>
       </c>
       <c r="R4" t="n">
-        <v>6962672</v>
+        <v>6962990</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119740791</v>
+        <v>119740056</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587344</v>
+        <v>587311</v>
       </c>
       <c r="R5" t="n">
-        <v>6962881</v>
+        <v>6962674</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119740485</v>
+        <v>119740791</v>
       </c>
       <c r="B6" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587301</v>
+        <v>587344</v>
       </c>
       <c r="R6" t="n">
-        <v>6962793</v>
+        <v>6962881</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119740472</v>
+        <v>119740508</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587294</v>
+        <v>587301</v>
       </c>
       <c r="R7" t="n">
-        <v>6962768</v>
+        <v>6962793</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119740756</v>
+        <v>119740075</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>91005</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,47 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587331</v>
+        <v>587322</v>
       </c>
       <c r="R8" t="n">
-        <v>6962854</v>
+        <v>6962672</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1413,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119741197</v>
+        <v>119740485</v>
       </c>
       <c r="B9" t="n">
         <v>90846</v>
@@ -1449,14 +1440,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587297</v>
+        <v>587301</v>
       </c>
       <c r="R9" t="n">
-        <v>6962990</v>
+        <v>6962793</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1515,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119740508</v>
+        <v>119740756</v>
       </c>
       <c r="B10" t="n">
-        <v>91005</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,38 +1518,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587301</v>
+        <v>587331</v>
       </c>
       <c r="R10" t="n">
-        <v>6962793</v>
+        <v>6962854</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119740056</v>
+        <v>119740092</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,21 +1633,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587311</v>
+        <v>587314</v>
       </c>
       <c r="R11" t="n">
         <v>6962674</v>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>119740472</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119741197</v>
+        <v>119740508</v>
       </c>
       <c r="B4" t="n">
-        <v>90846</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +901,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hattberget, Hattberget, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587297</v>
+        <v>587301</v>
       </c>
       <c r="R4" t="n">
-        <v>6962990</v>
+        <v>6962793</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119740056</v>
+        <v>119740075</v>
       </c>
       <c r="B5" t="n">
-        <v>90846</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587311</v>
+        <v>587322</v>
       </c>
       <c r="R5" t="n">
-        <v>6962674</v>
+        <v>6962672</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119740791</v>
+        <v>119740485</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödmyran, Rödmyran, Mpd</t>
+          <t>Husören, Husören, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587344</v>
+        <v>587301</v>
       </c>
       <c r="R6" t="n">
-        <v>6962881</v>
+        <v>6962793</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119740508</v>
+        <v>119740756</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1207,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Rödmyran, Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587301</v>
+        <v>587331</v>
       </c>
       <c r="R7" t="n">
-        <v>6962793</v>
+        <v>6962854</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1302,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119740075</v>
+        <v>119741197</v>
       </c>
       <c r="B8" t="n">
-        <v>91005</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,38 +1318,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Husören, Husören, Mpd</t>
+          <t>Hattberget, Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587322</v>
+        <v>587297</v>
       </c>
       <c r="R8" t="n">
-        <v>6962672</v>
+        <v>6962990</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1404,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119740485</v>
+        <v>119740056</v>
       </c>
       <c r="B9" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587301</v>
+        <v>587311</v>
       </c>
       <c r="R9" t="n">
-        <v>6962793</v>
+        <v>6962674</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119740756</v>
+        <v>119740791</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,31 +1526,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587331</v>
+        <v>587344</v>
       </c>
       <c r="R10" t="n">
-        <v>6962854</v>
+        <v>6962881</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1620,7 +1620,7 @@
         <v>119740092</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>119740791</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>119740791</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>119740791</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>119740791</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1717,6 +1717,103 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125897297</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100413</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>587309</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6962667</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1814,6 +1814,103 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125897332</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100510</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>587307</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6962673</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100510</v>
+        <v>100513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,6 +1910,3327 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125961707</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>587282</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6962896</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125957763</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>658</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>587323</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6962699</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125972596</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>587321</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6962845</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125972609</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>587337</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6962791</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125972598</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>587345</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6962976</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125962566</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>658</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>587288</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6962754</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125962085</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>587287</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6962808</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125972617</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>587321</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6962845</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125958439</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>587272</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6962788</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Talltitepar som matar ungar</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125958933</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>587305</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6962965</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125962027</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>587324</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6962796</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125961740</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>587266</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6962899</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125958715</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>587342</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6962882</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125957855</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>658</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>587332</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6962722</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125972611</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>658</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>587319</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6962816</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125958647</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>587329</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6962867</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125961919</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91520</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>658</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>587305</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6962821</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125962184</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>587287</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6962808</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125972597</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>587338</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6962986</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125958345</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>587332</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6962722</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125957718</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100420</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>587316</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6962676</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125961933</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>587299</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6962830</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125962209</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91678</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>587296</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6962809</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125958676</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>587316</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6962880</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125961753</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>587276</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6962874</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125961871</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>587271</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6962863</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125961128</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>587316</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6963012</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125961912</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>587290</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6962823</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125962228</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>587262</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6962805</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125972613</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>587283</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6962806</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125961825</v>
+      </c>
+      <c r="B44" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hattberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>587276</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6962874</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125962440</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>587288</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6962754</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -2629,48 +2629,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125972617</v>
+        <v>125958933</v>
       </c>
       <c r="B21" t="n">
-        <v>105355</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587321</v>
+        <v>587305</v>
       </c>
       <c r="R21" t="n">
-        <v>6962845</v>
+        <v>6962965</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2697,9 +2702,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2714,22 +2734,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125958439</v>
+        <v>125961740</v>
       </c>
       <c r="B22" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,43 +2757,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587272</v>
+        <v>587266</v>
       </c>
       <c r="R22" t="n">
-        <v>6962788</v>
+        <v>6962899</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2805,7 +2821,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2815,12 +2831,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2863,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125958933</v>
+        <v>125958439</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,27 +2874,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2887,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587305</v>
+        <v>587272</v>
       </c>
       <c r="R23" t="n">
-        <v>6962965</v>
+        <v>6962788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2942,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,12 +2952,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3071,53 +3091,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125961740</v>
+        <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>105355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587266</v>
+        <v>587321</v>
       </c>
       <c r="R25" t="n">
-        <v>6962899</v>
+        <v>6962845</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3144,24 +3159,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,12 +3176,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125958647</v>
+        <v>125961919</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>91520</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,39 +3510,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587329</v>
+        <v>587305</v>
       </c>
       <c r="R29" t="n">
-        <v>6962867</v>
+        <v>6962821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3572,24 +3567,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125961919</v>
+        <v>125962184</v>
       </c>
       <c r="B30" t="n">
-        <v>91520</v>
+        <v>91227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3651,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587305</v>
+        <v>587287</v>
       </c>
       <c r="R30" t="n">
-        <v>6962821</v>
+        <v>6962808</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3713,7 +3693,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125962184</v>
+        <v>125972597</v>
       </c>
       <c r="B31" t="n">
         <v>91227</v>
@@ -3744,17 +3724,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587287</v>
+        <v>587338</v>
       </c>
       <c r="R31" t="n">
-        <v>6962808</v>
+        <v>6962986</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3798,22 +3778,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125972597</v>
+        <v>125958647</v>
       </c>
       <c r="B32" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,37 +3801,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587338</v>
+        <v>587329</v>
       </c>
       <c r="R32" t="n">
-        <v>6962986</v>
+        <v>6962867</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3878,9 +3863,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3895,12 +3895,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100420</v>
+        <v>100421</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100513</v>
+        <v>100514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91520</v>
+        <v>91521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>125972596</v>
       </c>
       <c r="B16" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91520</v>
+        <v>91521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125972598</v>
+        <v>125962566</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>91521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,45 +2332,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587345</v>
+        <v>587288</v>
       </c>
       <c r="R18" t="n">
-        <v>6962976</v>
+        <v>6962754</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,11 +2392,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,22 +2406,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125962566</v>
+        <v>125972598</v>
       </c>
       <c r="B19" t="n">
-        <v>91520</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,37 +2429,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587288</v>
+        <v>587345</v>
       </c>
       <c r="R19" t="n">
-        <v>6962754</v>
+        <v>6962976</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,6 +2497,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,12 +2516,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125958933</v>
+        <v>125958439</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,27 +2640,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2669,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587305</v>
+        <v>587272</v>
       </c>
       <c r="R21" t="n">
-        <v>6962965</v>
+        <v>6962788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2714,12 +2718,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2746,53 +2750,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125961740</v>
+        <v>125972617</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>105356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587266</v>
+        <v>587321</v>
       </c>
       <c r="R22" t="n">
-        <v>6962899</v>
+        <v>6962845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,24 +2818,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2851,22 +2835,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125958439</v>
+        <v>125961740</v>
       </c>
       <c r="B23" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2874,43 +2858,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587272</v>
+        <v>587266</v>
       </c>
       <c r="R23" t="n">
-        <v>6962788</v>
+        <v>6962899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2952,12 +2932,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,48 +3071,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125972617</v>
+        <v>125958933</v>
       </c>
       <c r="B25" t="n">
-        <v>105355</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587321</v>
+        <v>587305</v>
       </c>
       <c r="R25" t="n">
-        <v>6962845</v>
+        <v>6962965</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3159,9 +3144,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,22 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125958715</v>
+        <v>125957855</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>91521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,39 +3199,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587342</v>
+        <v>587332</v>
       </c>
       <c r="R26" t="n">
-        <v>6962882</v>
+        <v>6962722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,24 +3256,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125957855</v>
+        <v>125958715</v>
       </c>
       <c r="B27" t="n">
-        <v>91520</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3316,34 +3296,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587332</v>
+        <v>587342</v>
       </c>
       <c r="R27" t="n">
-        <v>6962722</v>
+        <v>6962882</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,9 +3358,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91520</v>
+        <v>91521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>125961919</v>
       </c>
       <c r="B29" t="n">
-        <v>91520</v>
+        <v>91521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125962184</v>
+        <v>125972597</v>
       </c>
       <c r="B30" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,17 +3627,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587287</v>
+        <v>587338</v>
       </c>
       <c r="R30" t="n">
-        <v>6962808</v>
+        <v>6962986</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3681,22 +3681,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125972597</v>
+        <v>125962184</v>
       </c>
       <c r="B31" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,17 +3724,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587338</v>
+        <v>587287</v>
       </c>
       <c r="R31" t="n">
-        <v>6962986</v>
+        <v>6962808</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3778,12 +3778,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3907,49 +3907,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125958345</v>
+        <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>98331</v>
+        <v>91228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587332</v>
+        <v>587299</v>
       </c>
       <c r="R33" t="n">
-        <v>6962722</v>
+        <v>6962830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,19 +3975,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4018,45 +4004,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>100420</v>
+        <v>98332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R34" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4086,9 +4076,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,32 +4115,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125961933</v>
+        <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>91227</v>
+        <v>100421</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587299</v>
+        <v>587316</v>
       </c>
       <c r="R35" t="n">
-        <v>6962830</v>
+        <v>6962676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91678</v>
+        <v>91679</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125961128</v>
       </c>
       <c r="B40" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,52 +4838,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98331</v>
+        <v>98366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R42" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4927,60 +4923,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>98332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R43" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,57 +5024,61 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125961825</v>
+        <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>105355</v>
+        <v>98332</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587276</v>
+        <v>587288</v>
       </c>
       <c r="R44" t="n">
-        <v>6962874</v>
+        <v>6962754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5133,49 +5137,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125962440</v>
+        <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>98331</v>
+        <v>105356</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587288</v>
+        <v>587276</v>
       </c>
       <c r="R45" t="n">
-        <v>6962754</v>
+        <v>6962874</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5231,6 +5231,205 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126007568</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>587338</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6962927</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126007569</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tobidalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>587354</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6962937</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fyra stycken tiggande ungar</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100514</v>
+        <v>100516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>125962566</v>
       </c>
       <c r="B18" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125958439</v>
+        <v>125961740</v>
       </c>
       <c r="B21" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,43 +2640,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587272</v>
+        <v>587266</v>
       </c>
       <c r="R21" t="n">
-        <v>6962788</v>
+        <v>6962899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,7 +2704,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2718,12 +2714,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,48 +2746,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125972617</v>
+        <v>125962027</v>
       </c>
       <c r="B22" t="n">
-        <v>105356</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587321</v>
+        <v>587324</v>
       </c>
       <c r="R22" t="n">
-        <v>6962845</v>
+        <v>6962796</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2822,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,19 +2841,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125961740</v>
+        <v>125958933</v>
       </c>
       <c r="B23" t="n">
         <v>57651</v>
@@ -2883,14 +2889,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587266</v>
+        <v>587305</v>
       </c>
       <c r="R23" t="n">
-        <v>6962899</v>
+        <v>6962965</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2928,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2938,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2964,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125962027</v>
+        <v>125958439</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,27 +2981,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3004,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587324</v>
+        <v>587272</v>
       </c>
       <c r="R24" t="n">
-        <v>6962796</v>
+        <v>6962788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,14 +3047,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,53 +3091,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125958933</v>
+        <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>105358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587305</v>
+        <v>587321</v>
       </c>
       <c r="R25" t="n">
-        <v>6962965</v>
+        <v>6962845</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3144,24 +3159,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,12 +3176,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
         <v>125957855</v>
       </c>
       <c r="B26" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125961919</v>
+        <v>125972597</v>
       </c>
       <c r="B29" t="n">
-        <v>91521</v>
+        <v>91228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,37 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587305</v>
+        <v>587338</v>
       </c>
       <c r="R29" t="n">
-        <v>6962821</v>
+        <v>6962986</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3584,22 +3584,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125972597</v>
+        <v>125961919</v>
       </c>
       <c r="B30" t="n">
-        <v>91228</v>
+        <v>91524</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,37 +3607,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587338</v>
+        <v>587305</v>
       </c>
       <c r="R30" t="n">
-        <v>6962986</v>
+        <v>6962821</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3681,12 +3681,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4007,7 +4007,7 @@
         <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91679</v>
+        <v>91682</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,48 +4838,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B42" t="n">
-        <v>98366</v>
+        <v>98334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R42" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4923,64 +4927,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B43" t="n">
-        <v>98332</v>
+        <v>98368</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R43" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,61 +5024,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125962440</v>
+        <v>125961825</v>
       </c>
       <c r="B44" t="n">
-        <v>98332</v>
+        <v>105358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587288</v>
+        <v>587276</v>
       </c>
       <c r="R44" t="n">
-        <v>6962754</v>
+        <v>6962874</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5137,45 +5133,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125961825</v>
+        <v>125962440</v>
       </c>
       <c r="B45" t="n">
-        <v>105356</v>
+        <v>98334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587276</v>
+        <v>587288</v>
       </c>
       <c r="R45" t="n">
-        <v>6962874</v>
+        <v>6962754</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -3907,45 +3907,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125961933</v>
+        <v>125958345</v>
       </c>
       <c r="B33" t="n">
-        <v>91228</v>
+        <v>98334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587299</v>
+        <v>587332</v>
       </c>
       <c r="R33" t="n">
-        <v>6962830</v>
+        <v>6962722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3975,9 +3979,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4004,49 +4018,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B34" t="n">
-        <v>98334</v>
+        <v>100423</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R34" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,19 +4086,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,32 +4115,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125957718</v>
+        <v>125961933</v>
       </c>
       <c r="B35" t="n">
-        <v>100423</v>
+        <v>91228</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587316</v>
+        <v>587299</v>
       </c>
       <c r="R35" t="n">
-        <v>6962676</v>
+        <v>6962830</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>125972596</v>
       </c>
       <c r="B16" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125962566</v>
+        <v>125972598</v>
       </c>
       <c r="B18" t="n">
-        <v>91524</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,37 +2332,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587288</v>
+        <v>587345</v>
       </c>
       <c r="R18" t="n">
-        <v>6962754</v>
+        <v>6962976</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2392,6 +2400,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,22 +2419,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125972598</v>
+        <v>125962566</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>91528</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,45 +2442,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587345</v>
+        <v>587288</v>
       </c>
       <c r="R19" t="n">
-        <v>6962976</v>
+        <v>6962754</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,11 +2502,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,12 +2516,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2970,57 +2970,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125958439</v>
+        <v>125972617</v>
       </c>
       <c r="B24" t="n">
-        <v>57811</v>
+        <v>105362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587272</v>
+        <v>587321</v>
       </c>
       <c r="R24" t="n">
-        <v>6962788</v>
+        <v>6962845</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3047,24 +3038,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,60 +3055,69 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125972617</v>
+        <v>125958439</v>
       </c>
       <c r="B25" t="n">
-        <v>105358</v>
+        <v>57811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587321</v>
+        <v>587272</v>
       </c>
       <c r="R25" t="n">
-        <v>6962845</v>
+        <v>6962788</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3159,9 +3144,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,22 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125957855</v>
+        <v>125958715</v>
       </c>
       <c r="B26" t="n">
-        <v>91524</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,34 +3199,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587332</v>
+        <v>587342</v>
       </c>
       <c r="R26" t="n">
-        <v>6962722</v>
+        <v>6962882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3256,9 +3261,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125958715</v>
+        <v>125957855</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>91528</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,39 +3316,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587342</v>
+        <v>587332</v>
       </c>
       <c r="R27" t="n">
-        <v>6962882</v>
+        <v>6962722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,24 +3373,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>125972597</v>
       </c>
       <c r="B29" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125961919</v>
+        <v>125962184</v>
       </c>
       <c r="B30" t="n">
-        <v>91524</v>
+        <v>91232</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587305</v>
+        <v>587287</v>
       </c>
       <c r="R30" t="n">
-        <v>6962821</v>
+        <v>6962808</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125962184</v>
+        <v>125961919</v>
       </c>
       <c r="B31" t="n">
-        <v>91228</v>
+        <v>91528</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587287</v>
+        <v>587305</v>
       </c>
       <c r="R31" t="n">
-        <v>6962808</v>
+        <v>6962821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,49 +3907,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125958345</v>
+        <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587332</v>
+        <v>587299</v>
       </c>
       <c r="R33" t="n">
-        <v>6962722</v>
+        <v>6962830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,19 +3975,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4021,7 +4007,7 @@
         <v>125957718</v>
       </c>
       <c r="B34" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4115,45 +4101,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125961933</v>
+        <v>125958345</v>
       </c>
       <c r="B35" t="n">
-        <v>91228</v>
+        <v>98338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587299</v>
+        <v>587332</v>
       </c>
       <c r="R35" t="n">
-        <v>6962830</v>
+        <v>6962722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,9 +4173,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125961128</v>
       </c>
       <c r="B40" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,52 +4838,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98334</v>
+        <v>98372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R42" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4927,60 +4923,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98368</v>
+        <v>98338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R43" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,57 +5024,61 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125961825</v>
+        <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>105358</v>
+        <v>98338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587276</v>
+        <v>587288</v>
       </c>
       <c r="R44" t="n">
-        <v>6962874</v>
+        <v>6962754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5133,49 +5137,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125962440</v>
+        <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>98334</v>
+        <v>105362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587288</v>
+        <v>587276</v>
       </c>
       <c r="R45" t="n">
-        <v>6962754</v>
+        <v>6962874</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5237,7 +5237,7 @@
         <v>126007568</v>
       </c>
       <c r="B46" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125972598</v>
+        <v>125962566</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>91528</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,45 +2332,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587345</v>
+        <v>587288</v>
       </c>
       <c r="R18" t="n">
-        <v>6962976</v>
+        <v>6962754</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,11 +2392,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,22 +2406,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125962566</v>
+        <v>125972598</v>
       </c>
       <c r="B19" t="n">
-        <v>91528</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,37 +2429,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587288</v>
+        <v>587345</v>
       </c>
       <c r="R19" t="n">
-        <v>6962754</v>
+        <v>6962976</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,6 +2497,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,12 +2516,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2970,48 +2970,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125972617</v>
+        <v>125958439</v>
       </c>
       <c r="B24" t="n">
-        <v>105362</v>
+        <v>57811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587321</v>
+        <v>587272</v>
       </c>
       <c r="R24" t="n">
-        <v>6962845</v>
+        <v>6962788</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3038,9 +3047,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3055,69 +3079,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125958439</v>
+        <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>57811</v>
+        <v>105363</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587272</v>
+        <v>587321</v>
       </c>
       <c r="R25" t="n">
-        <v>6962788</v>
+        <v>6962845</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3144,24 +3159,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,12 +3176,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3907,45 +3907,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125961933</v>
+        <v>125958345</v>
       </c>
       <c r="B33" t="n">
-        <v>91232</v>
+        <v>98339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587299</v>
+        <v>587332</v>
       </c>
       <c r="R33" t="n">
-        <v>6962830</v>
+        <v>6962722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3975,9 +3979,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4007,7 +4021,7 @@
         <v>125957718</v>
       </c>
       <c r="B34" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4101,49 +4115,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125958345</v>
+        <v>125961933</v>
       </c>
       <c r="B35" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587332</v>
+        <v>587299</v>
       </c>
       <c r="R35" t="n">
-        <v>6962722</v>
+        <v>6962830</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,19 +4183,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,48 +4838,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B42" t="n">
-        <v>98372</v>
+        <v>98339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R42" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4923,64 +4927,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B43" t="n">
-        <v>98338</v>
+        <v>98373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R43" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,12 +5024,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
         <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125958715</v>
+        <v>125957855</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>91528</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,39 +3199,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587342</v>
+        <v>587332</v>
       </c>
       <c r="R26" t="n">
-        <v>6962882</v>
+        <v>6962722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,24 +3256,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125957855</v>
+        <v>125958715</v>
       </c>
       <c r="B27" t="n">
-        <v>91528</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3316,34 +3296,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587332</v>
+        <v>587342</v>
       </c>
       <c r="R27" t="n">
-        <v>6962722</v>
+        <v>6962882</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,9 +3358,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>125961707</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>125972596</v>
       </c>
       <c r="B16" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125962566</v>
+        <v>125972598</v>
       </c>
       <c r="B18" t="n">
-        <v>91528</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,37 +2332,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587288</v>
+        <v>587345</v>
       </c>
       <c r="R18" t="n">
-        <v>6962754</v>
+        <v>6962976</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2392,6 +2400,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,68 +2419,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125972598</v>
+        <v>125962085</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587345</v>
+        <v>587287</v>
       </c>
       <c r="R19" t="n">
-        <v>6962976</v>
+        <v>6962808</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,11 +2506,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,61 +2520,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125962085</v>
+        <v>125962566</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>91530</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587287</v>
+        <v>587288</v>
       </c>
       <c r="R20" t="n">
-        <v>6962808</v>
+        <v>6962754</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
         <v>125961740</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>125962027</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>125958933</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>125958439</v>
       </c>
       <c r="B24" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125957855</v>
+        <v>125958715</v>
       </c>
       <c r="B26" t="n">
-        <v>91528</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,34 +3199,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587332</v>
+        <v>587342</v>
       </c>
       <c r="R26" t="n">
-        <v>6962722</v>
+        <v>6962882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3256,9 +3261,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125958715</v>
+        <v>125957855</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>91530</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,39 +3316,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587342</v>
+        <v>587332</v>
       </c>
       <c r="R27" t="n">
-        <v>6962882</v>
+        <v>6962722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,24 +3373,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125972597</v>
+        <v>125958647</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,37 +3510,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587338</v>
+        <v>587329</v>
       </c>
       <c r="R29" t="n">
-        <v>6962986</v>
+        <v>6962867</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3567,9 +3572,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,22 +3604,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125962184</v>
+        <v>125972597</v>
       </c>
       <c r="B30" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,17 +3647,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587287</v>
+        <v>587338</v>
       </c>
       <c r="R30" t="n">
-        <v>6962808</v>
+        <v>6962986</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3681,22 +3701,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125961919</v>
+        <v>125962184</v>
       </c>
       <c r="B31" t="n">
-        <v>91528</v>
+        <v>91234</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587305</v>
+        <v>587287</v>
       </c>
       <c r="R31" t="n">
-        <v>6962821</v>
+        <v>6962808</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125958647</v>
+        <v>125961919</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>91530</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,39 +3821,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587329</v>
+        <v>587305</v>
       </c>
       <c r="R32" t="n">
-        <v>6962867</v>
+        <v>6962821</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3863,24 +3878,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3907,49 +3907,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125958345</v>
+        <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>98339</v>
+        <v>91234</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587332</v>
+        <v>587299</v>
       </c>
       <c r="R33" t="n">
-        <v>6962722</v>
+        <v>6962830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,19 +3975,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4018,45 +4004,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>100428</v>
+        <v>98341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R34" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4086,9 +4076,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,32 +4115,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125961933</v>
+        <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>91232</v>
+        <v>100430</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587299</v>
+        <v>587316</v>
       </c>
       <c r="R35" t="n">
-        <v>6962830</v>
+        <v>6962676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>125958676</v>
       </c>
       <c r="B37" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>125961871</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125961128</v>
       </c>
       <c r="B40" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98373</v>
+        <v>98375</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,52 +4838,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98339</v>
+        <v>98375</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R42" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4927,60 +4923,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98373</v>
+        <v>98341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R43" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,12 +5024,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
         <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>126007568</v>
       </c>
       <c r="B46" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>126007569</v>
       </c>
       <c r="B47" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>125972596</v>
       </c>
       <c r="B16" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125972598</v>
+        <v>125962566</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>91532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,45 +2332,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587345</v>
+        <v>587288</v>
       </c>
       <c r="R18" t="n">
-        <v>6962976</v>
+        <v>6962754</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,11 +2392,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,64 +2406,68 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125962085</v>
+        <v>125972598</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587287</v>
+        <v>587345</v>
       </c>
       <c r="R19" t="n">
-        <v>6962808</v>
+        <v>6962976</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2506,6 +2497,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,57 +2516,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125962566</v>
+        <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>91530</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587288</v>
+        <v>587287</v>
       </c>
       <c r="R20" t="n">
-        <v>6962754</v>
+        <v>6962808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125961740</v>
+        <v>125958439</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57812</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,39 +2640,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587266</v>
+        <v>587272</v>
       </c>
       <c r="R21" t="n">
-        <v>6962899</v>
+        <v>6962788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2714,12 +2718,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2746,53 +2750,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125962027</v>
+        <v>125972617</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>105367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587324</v>
+        <v>587321</v>
       </c>
       <c r="R22" t="n">
-        <v>6962796</v>
+        <v>6962845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,19 +2835,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125958933</v>
+        <v>125961740</v>
       </c>
       <c r="B23" t="n">
         <v>57652</v>
@@ -2889,14 +2883,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587305</v>
+        <v>587266</v>
       </c>
       <c r="R23" t="n">
-        <v>6962965</v>
+        <v>6962899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2938,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2970,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125958439</v>
+        <v>125962027</v>
       </c>
       <c r="B24" t="n">
-        <v>57812</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,31 +2975,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3014,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587272</v>
+        <v>587324</v>
       </c>
       <c r="R24" t="n">
-        <v>6962788</v>
+        <v>6962796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,24 +3037,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3091,48 +3071,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125972617</v>
+        <v>125958933</v>
       </c>
       <c r="B25" t="n">
-        <v>105365</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587321</v>
+        <v>587305</v>
       </c>
       <c r="R25" t="n">
-        <v>6962845</v>
+        <v>6962965</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3159,9 +3144,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,22 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125958715</v>
+        <v>125957855</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>91532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,39 +3199,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587342</v>
+        <v>587332</v>
       </c>
       <c r="R26" t="n">
-        <v>6962882</v>
+        <v>6962722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,24 +3256,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125957855</v>
+        <v>125958715</v>
       </c>
       <c r="B27" t="n">
-        <v>91530</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3316,34 +3296,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587332</v>
+        <v>587342</v>
       </c>
       <c r="R27" t="n">
-        <v>6962722</v>
+        <v>6962882</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,9 +3358,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>125972597</v>
       </c>
       <c r="B30" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>125962184</v>
       </c>
       <c r="B31" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>125961919</v>
       </c>
       <c r="B32" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125961933</v>
+        <v>125957718</v>
       </c>
       <c r="B33" t="n">
-        <v>91234</v>
+        <v>100432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587299</v>
+        <v>587316</v>
       </c>
       <c r="R33" t="n">
-        <v>6962830</v>
+        <v>6962676</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,49 +4004,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125958345</v>
+        <v>125961933</v>
       </c>
       <c r="B34" t="n">
-        <v>98341</v>
+        <v>91236</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587332</v>
+        <v>587299</v>
       </c>
       <c r="R34" t="n">
-        <v>6962722</v>
+        <v>6962830</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,19 +4072,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,45 +4101,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B35" t="n">
-        <v>100430</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R35" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,9 +4173,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125961128</v>
       </c>
       <c r="B40" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,48 +4838,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B42" t="n">
-        <v>98375</v>
+        <v>98343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R42" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4923,64 +4927,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B43" t="n">
-        <v>98341</v>
+        <v>98377</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R43" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,61 +5024,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125962440</v>
+        <v>125961825</v>
       </c>
       <c r="B44" t="n">
-        <v>98341</v>
+        <v>105367</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587288</v>
+        <v>587276</v>
       </c>
       <c r="R44" t="n">
-        <v>6962754</v>
+        <v>6962874</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5137,45 +5133,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125961825</v>
+        <v>125962440</v>
       </c>
       <c r="B45" t="n">
-        <v>105365</v>
+        <v>98343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587276</v>
+        <v>587288</v>
       </c>
       <c r="R45" t="n">
-        <v>6962874</v>
+        <v>6962754</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5237,7 +5237,7 @@
         <v>126007568</v>
       </c>
       <c r="B46" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125958647</v>
+        <v>125972597</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>91236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,42 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587329</v>
+        <v>587338</v>
       </c>
       <c r="R29" t="n">
-        <v>6962867</v>
+        <v>6962986</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3572,24 +3567,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,19 +3584,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125972597</v>
+        <v>125962184</v>
       </c>
       <c r="B30" t="n">
         <v>91236</v>
@@ -3647,17 +3627,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587338</v>
+        <v>587287</v>
       </c>
       <c r="R30" t="n">
-        <v>6962986</v>
+        <v>6962808</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3701,22 +3681,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125962184</v>
+        <v>125961919</v>
       </c>
       <c r="B31" t="n">
-        <v>91236</v>
+        <v>91532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,21 +3704,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3748,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587287</v>
+        <v>587305</v>
       </c>
       <c r="R31" t="n">
-        <v>6962808</v>
+        <v>6962821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3810,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125961919</v>
+        <v>125958647</v>
       </c>
       <c r="B32" t="n">
-        <v>91532</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,34 +3801,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587305</v>
+        <v>587329</v>
       </c>
       <c r="R32" t="n">
-        <v>6962821</v>
+        <v>6962867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,9 +3863,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125957718</v>
+        <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>100432</v>
+        <v>91236</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587316</v>
+        <v>587299</v>
       </c>
       <c r="R33" t="n">
-        <v>6962676</v>
+        <v>6962830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,45 +4004,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125961933</v>
+        <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>91236</v>
+        <v>98343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587299</v>
+        <v>587332</v>
       </c>
       <c r="R34" t="n">
-        <v>6962830</v>
+        <v>6962722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4072,9 +4076,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4101,49 +4115,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>100432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R35" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,19 +4183,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4838,52 +4838,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98343</v>
+        <v>98377</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R42" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4927,60 +4923,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98377</v>
+        <v>98343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R43" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,12 +5024,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>125972596</v>
       </c>
       <c r="B16" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>125962566</v>
       </c>
       <c r="B18" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125958439</v>
+        <v>125961740</v>
       </c>
       <c r="B21" t="n">
-        <v>57812</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,43 +2640,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587272</v>
+        <v>587266</v>
       </c>
       <c r="R21" t="n">
-        <v>6962788</v>
+        <v>6962899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,7 +2704,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2718,12 +2714,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2753,7 +2749,7 @@
         <v>125972617</v>
       </c>
       <c r="B22" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,7 +2843,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125961740</v>
+        <v>125962027</v>
       </c>
       <c r="B23" t="n">
         <v>57652</v>
@@ -2883,14 +2879,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587266</v>
+        <v>587324</v>
       </c>
       <c r="R23" t="n">
-        <v>6962899</v>
+        <v>6962796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,19 +2916,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2964,7 +2950,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125962027</v>
+        <v>125958933</v>
       </c>
       <c r="B24" t="n">
         <v>57652</v>
@@ -3004,10 +2990,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587324</v>
+        <v>587305</v>
       </c>
       <c r="R24" t="n">
-        <v>6962796</v>
+        <v>6962965</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,9 +3023,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3071,10 +3067,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125958933</v>
+        <v>125958439</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>57812</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,27 +3078,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587305</v>
+        <v>587272</v>
       </c>
       <c r="R25" t="n">
-        <v>6962965</v>
+        <v>6962788</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3191,7 +3191,7 @@
         <v>125957855</v>
       </c>
       <c r="B26" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>125972597</v>
       </c>
       <c r="B29" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125962184</v>
       </c>
       <c r="B30" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125961919</v>
       </c>
       <c r="B31" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,49 +4004,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B34" t="n">
-        <v>98343</v>
+        <v>100434</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R34" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,19 +4072,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,45 +4101,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B35" t="n">
-        <v>100432</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R35" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,9 +4173,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125961128</v>
       </c>
       <c r="B40" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5036,45 +5036,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125961825</v>
+        <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>105367</v>
+        <v>98345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587276</v>
+        <v>587288</v>
       </c>
       <c r="R44" t="n">
-        <v>6962874</v>
+        <v>6962754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5133,49 +5137,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125962440</v>
+        <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>98343</v>
+        <v>105371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>587288</v>
+        <v>587276</v>
       </c>
       <c r="R45" t="n">
-        <v>6962754</v>
+        <v>6962874</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5237,7 +5237,7 @@
         <v>126007568</v>
       </c>
       <c r="B46" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125962566</v>
+        <v>125972598</v>
       </c>
       <c r="B18" t="n">
-        <v>91534</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,37 +2332,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587288</v>
+        <v>587345</v>
       </c>
       <c r="R18" t="n">
-        <v>6962754</v>
+        <v>6962976</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2392,6 +2400,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,22 +2419,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125972598</v>
+        <v>125962566</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>91534</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,45 +2442,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587345</v>
+        <v>587288</v>
       </c>
       <c r="R19" t="n">
-        <v>6962976</v>
+        <v>6962754</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,11 +2502,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,12 +2516,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125972597</v>
+        <v>125958647</v>
       </c>
       <c r="B29" t="n">
-        <v>91238</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,37 +3510,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587338</v>
+        <v>587329</v>
       </c>
       <c r="R29" t="n">
-        <v>6962986</v>
+        <v>6962867</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3567,9 +3572,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,19 +3604,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125962184</v>
+        <v>125972597</v>
       </c>
       <c r="B30" t="n">
         <v>91238</v>
@@ -3627,17 +3647,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587287</v>
+        <v>587338</v>
       </c>
       <c r="R30" t="n">
-        <v>6962808</v>
+        <v>6962986</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3681,22 +3701,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125961919</v>
+        <v>125962184</v>
       </c>
       <c r="B31" t="n">
-        <v>91534</v>
+        <v>91238</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587305</v>
+        <v>587287</v>
       </c>
       <c r="R31" t="n">
-        <v>6962821</v>
+        <v>6962808</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125958647</v>
+        <v>125961919</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>91534</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,39 +3821,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587329</v>
+        <v>587305</v>
       </c>
       <c r="R32" t="n">
-        <v>6962867</v>
+        <v>6962821</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3863,24 +3878,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>125961707</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>125972596</v>
       </c>
       <c r="B16" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125972598</v>
+        <v>125962566</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>91538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,45 +2332,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587345</v>
+        <v>587288</v>
       </c>
       <c r="R18" t="n">
-        <v>6962976</v>
+        <v>6962754</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,11 +2392,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,22 +2406,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125962566</v>
+        <v>125972598</v>
       </c>
       <c r="B19" t="n">
-        <v>91534</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,37 +2429,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587288</v>
+        <v>587345</v>
       </c>
       <c r="R19" t="n">
-        <v>6962754</v>
+        <v>6962976</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,6 +2497,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,12 +2516,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2531,7 +2531,7 @@
         <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>125961740</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,48 +2746,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125972617</v>
+        <v>125962027</v>
       </c>
       <c r="B22" t="n">
-        <v>105371</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587321</v>
+        <v>587324</v>
       </c>
       <c r="R22" t="n">
-        <v>6962845</v>
+        <v>6962796</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,6 +2822,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2831,22 +2841,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125962027</v>
+        <v>125958933</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587324</v>
+        <v>587305</v>
       </c>
       <c r="R23" t="n">
-        <v>6962796</v>
+        <v>6962965</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2916,9 +2926,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2950,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125958933</v>
+        <v>125958439</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2961,27 +2981,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2990,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587305</v>
+        <v>587272</v>
       </c>
       <c r="R24" t="n">
-        <v>6962965</v>
+        <v>6962788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3025,7 +3049,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3035,12 +3059,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3067,57 +3091,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125958439</v>
+        <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>57812</v>
+        <v>105384</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587272</v>
+        <v>587321</v>
       </c>
       <c r="R25" t="n">
-        <v>6962788</v>
+        <v>6962845</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3144,24 +3159,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,12 +3176,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
         <v>125957855</v>
       </c>
       <c r="B26" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>125958715</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125958647</v>
+        <v>125972597</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>91242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,42 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587329</v>
+        <v>587338</v>
       </c>
       <c r="R29" t="n">
-        <v>6962867</v>
+        <v>6962986</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3572,24 +3567,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,22 +3584,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125972597</v>
+        <v>125962184</v>
       </c>
       <c r="B30" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3647,17 +3627,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587338</v>
+        <v>587287</v>
       </c>
       <c r="R30" t="n">
-        <v>6962986</v>
+        <v>6962808</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3701,22 +3681,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125962184</v>
+        <v>125961919</v>
       </c>
       <c r="B31" t="n">
-        <v>91238</v>
+        <v>91538</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,21 +3704,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3748,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587287</v>
+        <v>587305</v>
       </c>
       <c r="R31" t="n">
-        <v>6962808</v>
+        <v>6962821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3810,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125961919</v>
+        <v>125958647</v>
       </c>
       <c r="B32" t="n">
-        <v>91534</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,34 +3801,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587305</v>
+        <v>587329</v>
       </c>
       <c r="R32" t="n">
-        <v>6962821</v>
+        <v>6962867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,9 +3863,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3910,7 +3910,7 @@
         <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,45 +4004,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>100434</v>
+        <v>98349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R34" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4072,9 +4076,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4101,49 +4115,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>100438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R35" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,19 +4183,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>125958676</v>
       </c>
       <c r="B37" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>125961871</v>
       </c>
       <c r="B39" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125961128</v>
       </c>
       <c r="B40" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>126007568</v>
       </c>
       <c r="B46" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>126007569</v>
       </c>
       <c r="B47" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125972597</v>
+        <v>125958647</v>
       </c>
       <c r="B29" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,37 +3510,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587338</v>
+        <v>587329</v>
       </c>
       <c r="R29" t="n">
-        <v>6962986</v>
+        <v>6962867</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3567,9 +3572,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,19 +3604,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125962184</v>
+        <v>125972597</v>
       </c>
       <c r="B30" t="n">
         <v>91242</v>
@@ -3627,17 +3647,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587287</v>
+        <v>587338</v>
       </c>
       <c r="R30" t="n">
-        <v>6962808</v>
+        <v>6962986</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3681,22 +3701,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125961919</v>
+        <v>125962184</v>
       </c>
       <c r="B31" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587305</v>
+        <v>587287</v>
       </c>
       <c r="R31" t="n">
-        <v>6962821</v>
+        <v>6962808</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125958647</v>
+        <v>125961919</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>91538</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,39 +3821,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587329</v>
+        <v>587305</v>
       </c>
       <c r="R32" t="n">
-        <v>6962867</v>
+        <v>6962821</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3863,24 +3878,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125962566</v>
+        <v>125972598</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,37 +2332,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587288</v>
+        <v>587345</v>
       </c>
       <c r="R18" t="n">
-        <v>6962754</v>
+        <v>6962976</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2392,6 +2400,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,68 +2419,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125972598</v>
+        <v>125962085</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587345</v>
+        <v>587287</v>
       </c>
       <c r="R19" t="n">
-        <v>6962976</v>
+        <v>6962808</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,11 +2506,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,61 +2520,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125962085</v>
+        <v>125962566</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>91538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587287</v>
+        <v>587288</v>
       </c>
       <c r="R20" t="n">
-        <v>6962808</v>
+        <v>6962754</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125961740</v>
+        <v>125958439</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,39 +2640,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587266</v>
+        <v>587272</v>
       </c>
       <c r="R21" t="n">
-        <v>6962899</v>
+        <v>6962788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2714,12 +2718,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2746,53 +2750,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125962027</v>
+        <v>125972617</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>105387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587324</v>
+        <v>587321</v>
       </c>
       <c r="R22" t="n">
-        <v>6962796</v>
+        <v>6962845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,19 +2835,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125958933</v>
+        <v>125961740</v>
       </c>
       <c r="B23" t="n">
         <v>57656</v>
@@ -2889,14 +2883,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587305</v>
+        <v>587266</v>
       </c>
       <c r="R23" t="n">
-        <v>6962965</v>
+        <v>6962899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2938,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2970,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125958439</v>
+        <v>125962027</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,31 +2975,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3014,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587272</v>
+        <v>587324</v>
       </c>
       <c r="R24" t="n">
-        <v>6962788</v>
+        <v>6962796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,24 +3037,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3091,48 +3071,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125972617</v>
+        <v>125958933</v>
       </c>
       <c r="B25" t="n">
-        <v>105387</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587321</v>
+        <v>587305</v>
       </c>
       <c r="R25" t="n">
-        <v>6962845</v>
+        <v>6962965</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3159,9 +3144,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,22 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125957855</v>
+        <v>125958715</v>
       </c>
       <c r="B26" t="n">
-        <v>91538</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,34 +3199,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587332</v>
+        <v>587342</v>
       </c>
       <c r="R26" t="n">
-        <v>6962722</v>
+        <v>6962882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3256,9 +3261,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125958715</v>
+        <v>125957855</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>91538</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,39 +3316,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587342</v>
+        <v>587332</v>
       </c>
       <c r="R27" t="n">
-        <v>6962882</v>
+        <v>6962722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,24 +3373,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125962184</v>
+        <v>125961919</v>
       </c>
       <c r="B31" t="n">
-        <v>91242</v>
+        <v>91538</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587287</v>
+        <v>587305</v>
       </c>
       <c r="R31" t="n">
-        <v>6962808</v>
+        <v>6962821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125961919</v>
+        <v>125962184</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587305</v>
+        <v>587287</v>
       </c>
       <c r="R32" t="n">
-        <v>6962821</v>
+        <v>6962808</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4004,49 +4004,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B34" t="n">
-        <v>98352</v>
+        <v>100441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R34" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,19 +4072,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,45 +4101,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B35" t="n">
-        <v>100441</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R35" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,9 +4173,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4838,48 +4838,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B42" t="n">
-        <v>98386</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R42" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4923,64 +4927,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>98386</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R43" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,12 +5024,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -1722,7 +1722,7 @@
         <v>125897297</v>
       </c>
       <c r="B12" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>125897332</v>
       </c>
       <c r="B13" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>125961707</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>125957763</v>
       </c>
       <c r="B15" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>125972596</v>
       </c>
       <c r="B16" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>125972609</v>
       </c>
       <c r="B17" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125972598</v>
+        <v>125962566</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>91541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,45 +2332,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587345</v>
+        <v>587288</v>
       </c>
       <c r="R18" t="n">
-        <v>6962976</v>
+        <v>6962754</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,11 +2392,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,64 +2406,68 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125962085</v>
+        <v>125972598</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587287</v>
+        <v>587345</v>
       </c>
       <c r="R19" t="n">
-        <v>6962808</v>
+        <v>6962976</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2506,6 +2497,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,57 +2516,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125962566</v>
+        <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>91538</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587288</v>
+        <v>587287</v>
       </c>
       <c r="R20" t="n">
-        <v>6962754</v>
+        <v>6962808</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125958439</v>
+        <v>125961740</v>
       </c>
       <c r="B21" t="n">
-        <v>57816</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,43 +2640,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587272</v>
+        <v>587266</v>
       </c>
       <c r="R21" t="n">
-        <v>6962788</v>
+        <v>6962899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,7 +2704,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2718,12 +2714,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,48 +2746,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125972617</v>
+        <v>125962027</v>
       </c>
       <c r="B22" t="n">
-        <v>105387</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587321</v>
+        <v>587324</v>
       </c>
       <c r="R22" t="n">
-        <v>6962845</v>
+        <v>6962796</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2822,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,22 +2841,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125961740</v>
+        <v>125958933</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,14 +2889,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587266</v>
+        <v>587305</v>
       </c>
       <c r="R23" t="n">
-        <v>6962899</v>
+        <v>6962965</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2928,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2938,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2964,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125962027</v>
+        <v>125958439</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,27 +2981,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3004,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587324</v>
+        <v>587272</v>
       </c>
       <c r="R24" t="n">
-        <v>6962796</v>
+        <v>6962788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,14 +3047,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,53 +3091,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125958933</v>
+        <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>105396</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587305</v>
+        <v>587321</v>
       </c>
       <c r="R25" t="n">
-        <v>6962965</v>
+        <v>6962845</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3144,24 +3159,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,22 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125958715</v>
+        <v>125957855</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>91541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,39 +3199,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587342</v>
+        <v>587332</v>
       </c>
       <c r="R26" t="n">
-        <v>6962882</v>
+        <v>6962722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,24 +3256,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3305,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125957855</v>
+        <v>125958715</v>
       </c>
       <c r="B27" t="n">
-        <v>91538</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3316,34 +3296,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587332</v>
+        <v>587342</v>
       </c>
       <c r="R27" t="n">
-        <v>6962722</v>
+        <v>6962882</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,9 +3358,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3405,7 +3405,7 @@
         <v>125972611</v>
       </c>
       <c r="B28" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125958647</v>
+        <v>125972597</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,42 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587329</v>
+        <v>587338</v>
       </c>
       <c r="R29" t="n">
-        <v>6962867</v>
+        <v>6962986</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3572,24 +3567,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,22 +3584,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125972597</v>
+        <v>125962184</v>
       </c>
       <c r="B30" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3647,17 +3627,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587338</v>
+        <v>587287</v>
       </c>
       <c r="R30" t="n">
-        <v>6962986</v>
+        <v>6962808</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3701,12 +3681,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3716,7 +3696,7 @@
         <v>125961919</v>
       </c>
       <c r="B31" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3810,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125962184</v>
+        <v>125958647</v>
       </c>
       <c r="B32" t="n">
-        <v>91242</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,34 +3801,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587287</v>
+        <v>587329</v>
       </c>
       <c r="R32" t="n">
-        <v>6962808</v>
+        <v>6962867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,9 +3863,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3910,7 +3910,7 @@
         <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4004,45 +4004,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>100441</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R34" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4072,9 +4076,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4101,49 +4115,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>98352</v>
+        <v>100450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R35" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,19 +4183,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4215,7 +4215,7 @@
         <v>125962209</v>
       </c>
       <c r="B36" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>125958676</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>125961753</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>125961871</v>
       </c>
       <c r="B39" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>125961128</v>
       </c>
       <c r="B40" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>125961912</v>
       </c>
       <c r="B41" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,52 +4838,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98395</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R42" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4927,60 +4923,64 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B43" t="n">
-        <v>98386</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R43" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,12 +5024,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
         <v>125962440</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>125961825</v>
       </c>
       <c r="B45" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>126007568</v>
       </c>
       <c r="B46" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>126007569</v>
       </c>
       <c r="B47" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125972597</v>
+        <v>125958647</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,37 +3510,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587338</v>
+        <v>587329</v>
       </c>
       <c r="R29" t="n">
-        <v>6962986</v>
+        <v>6962867</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3567,9 +3572,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,19 +3604,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125962184</v>
+        <v>125972597</v>
       </c>
       <c r="B30" t="n">
         <v>91245</v>
@@ -3627,17 +3647,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587287</v>
+        <v>587338</v>
       </c>
       <c r="R30" t="n">
-        <v>6962808</v>
+        <v>6962986</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3681,22 +3701,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125961919</v>
+        <v>125962184</v>
       </c>
       <c r="B31" t="n">
-        <v>91541</v>
+        <v>91245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587305</v>
+        <v>587287</v>
       </c>
       <c r="R31" t="n">
-        <v>6962821</v>
+        <v>6962808</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125958647</v>
+        <v>125961919</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>91541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3801,39 +3821,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587329</v>
+        <v>587305</v>
       </c>
       <c r="R32" t="n">
-        <v>6962867</v>
+        <v>6962821</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3863,24 +3878,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4004,49 +4004,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>100450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R34" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4076,19 +4072,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4115,45 +4101,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125957718</v>
+        <v>125958345</v>
       </c>
       <c r="B35" t="n">
-        <v>100450</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587316</v>
+        <v>587332</v>
       </c>
       <c r="R35" t="n">
-        <v>6962676</v>
+        <v>6962722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,9 +4173,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125958647</v>
+        <v>125972597</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3510,42 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587329</v>
+        <v>587338</v>
       </c>
       <c r="R29" t="n">
-        <v>6962867</v>
+        <v>6962986</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3572,24 +3567,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,19 +3584,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125972597</v>
+        <v>125962184</v>
       </c>
       <c r="B30" t="n">
         <v>91245</v>
@@ -3647,17 +3627,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587338</v>
+        <v>587287</v>
       </c>
       <c r="R30" t="n">
-        <v>6962986</v>
+        <v>6962808</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3701,22 +3681,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125962184</v>
+        <v>125961919</v>
       </c>
       <c r="B31" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,21 +3704,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3748,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587287</v>
+        <v>587305</v>
       </c>
       <c r="R31" t="n">
-        <v>6962808</v>
+        <v>6962821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3810,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125961919</v>
+        <v>125958647</v>
       </c>
       <c r="B32" t="n">
-        <v>91541</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3821,34 +3801,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587305</v>
+        <v>587329</v>
       </c>
       <c r="R32" t="n">
-        <v>6962821</v>
+        <v>6962867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,9 +3863,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125961933</v>
+        <v>125957718</v>
       </c>
       <c r="B33" t="n">
-        <v>91245</v>
+        <v>100450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587299</v>
+        <v>587316</v>
       </c>
       <c r="R33" t="n">
-        <v>6962830</v>
+        <v>6962676</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125957718</v>
+        <v>125961933</v>
       </c>
       <c r="B34" t="n">
-        <v>100450</v>
+        <v>91245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587316</v>
+        <v>587299</v>
       </c>
       <c r="R34" t="n">
-        <v>6962676</v>
+        <v>6962830</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4838,48 +4838,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125972613</v>
+        <v>125962228</v>
       </c>
       <c r="B42" t="n">
-        <v>98395</v>
+        <v>98361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587283</v>
+        <v>587262</v>
       </c>
       <c r="R42" t="n">
-        <v>6962806</v>
+        <v>6962805</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4923,64 +4927,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125962228</v>
+        <v>125972613</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>98395</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587262</v>
+        <v>587283</v>
       </c>
       <c r="R43" t="n">
-        <v>6962805</v>
+        <v>6962806</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5024,12 +5024,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -2418,56 +2418,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125972598</v>
+        <v>125962085</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587345</v>
+        <v>587287</v>
       </c>
       <c r="R19" t="n">
-        <v>6962976</v>
+        <v>6962808</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,11 +2493,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,64 +2507,68 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125962085</v>
+        <v>125972598</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587287</v>
+        <v>587345</v>
       </c>
       <c r="R20" t="n">
-        <v>6962808</v>
+        <v>6962976</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2603,6 +2598,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2617,12 +2617,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -2418,52 +2418,56 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125962085</v>
+        <v>125972598</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587287</v>
+        <v>587345</v>
       </c>
       <c r="R19" t="n">
-        <v>6962808</v>
+        <v>6962976</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2493,6 +2497,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2507,68 +2516,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125972598</v>
+        <v>125962085</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587345</v>
+        <v>587287</v>
       </c>
       <c r="R20" t="n">
-        <v>6962976</v>
+        <v>6962808</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2598,11 +2603,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2617,22 +2617,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125961740</v>
+        <v>125958439</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,39 +2640,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587266</v>
+        <v>587272</v>
       </c>
       <c r="R21" t="n">
-        <v>6962899</v>
+        <v>6962788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2714,12 +2718,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2746,53 +2750,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125962027</v>
+        <v>125972617</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>105396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587324</v>
+        <v>587321</v>
       </c>
       <c r="R22" t="n">
-        <v>6962796</v>
+        <v>6962845</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,19 +2835,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125958933</v>
+        <v>125961740</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2889,14 +2883,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587305</v>
+        <v>587266</v>
       </c>
       <c r="R23" t="n">
-        <v>6962965</v>
+        <v>6962899</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2938,7 +2932,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2970,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125958439</v>
+        <v>125962027</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,31 +2975,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3014,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587272</v>
+        <v>587324</v>
       </c>
       <c r="R24" t="n">
-        <v>6962788</v>
+        <v>6962796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,24 +3037,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3091,48 +3071,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125972617</v>
+        <v>125958933</v>
       </c>
       <c r="B25" t="n">
-        <v>105396</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587321</v>
+        <v>587305</v>
       </c>
       <c r="R25" t="n">
-        <v>6962845</v>
+        <v>6962965</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3159,9 +3144,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,12 +3176,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3907,32 +3907,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125957718</v>
+        <v>125961933</v>
       </c>
       <c r="B33" t="n">
-        <v>100450</v>
+        <v>91245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587316</v>
+        <v>587299</v>
       </c>
       <c r="R33" t="n">
-        <v>6962676</v>
+        <v>6962830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,45 +4004,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125961933</v>
+        <v>125958345</v>
       </c>
       <c r="B34" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587299</v>
+        <v>587332</v>
       </c>
       <c r="R34" t="n">
-        <v>6962830</v>
+        <v>6962722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4072,9 +4076,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4101,49 +4115,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125958345</v>
+        <v>125957718</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>100450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587332</v>
+        <v>587316</v>
       </c>
       <c r="R35" t="n">
-        <v>6962722</v>
+        <v>6962676</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4173,19 +4183,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 35913-2021 artfynd.xlsx
+++ b/artfynd/A 35913-2021 artfynd.xlsx
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125958439</v>
+        <v>125961740</v>
       </c>
       <c r="B21" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2640,43 +2640,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Hattberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587272</v>
+        <v>587266</v>
       </c>
       <c r="R21" t="n">
-        <v>6962788</v>
+        <v>6962899</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,7 +2704,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2718,12 +2714,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Talltitepar som matar ungar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,48 +2746,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125972617</v>
+        <v>125962027</v>
       </c>
       <c r="B22" t="n">
-        <v>105396</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587321</v>
+        <v>587324</v>
       </c>
       <c r="R22" t="n">
-        <v>6962845</v>
+        <v>6962796</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2821,6 +2822,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,19 +2841,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125961740</v>
+        <v>125958933</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2883,14 +2889,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hattberget, Mpd</t>
+          <t>Tobidalen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587266</v>
+        <v>587305</v>
       </c>
       <c r="R23" t="n">
-        <v>6962899</v>
+        <v>6962965</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,7 +2928,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2932,7 +2938,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2964,10 +2970,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125962027</v>
+        <v>125958439</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2975,27 +2981,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3004,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587324</v>
+        <v>587272</v>
       </c>
       <c r="R24" t="n">
-        <v>6962796</v>
+        <v>6962788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,14 +3047,24 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Talltitepar som matar ungar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,53 +3091,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125958933</v>
+        <v>125972617</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>105396</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tobidalen, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587305</v>
+        <v>587321</v>
       </c>
       <c r="R25" t="n">
-        <v>6962965</v>
+        <v>6962845</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3144,24 +3159,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,12 +3176,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
